--- a/flowsheet_units.xlsx
+++ b/flowsheet_units.xlsx
@@ -630,10 +630,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>3.268202108648651</v>
+        <v>3.268202108648652</v>
       </c>
       <c r="G14" t="n">
-        <v>58.87666098730544</v>
+        <v>58.87666098730547</v>
       </c>
     </row>
     <row r="15">
@@ -659,10 +659,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1236522636382453</v>
+        <v>0.1236797910719729</v>
       </c>
       <c r="G15" t="n">
-        <v>2.227595529442989</v>
+        <v>2.228091436161592</v>
       </c>
     </row>
     <row r="17">
@@ -733,10 +733,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>3.391854372286896</v>
+        <v>3.391881899720625</v>
       </c>
       <c r="G19" t="n">
-        <v>61.10425651674843</v>
+        <v>61.10475242346707</v>
       </c>
     </row>
   </sheetData>
@@ -905,10 +905,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>4.885365103802371</v>
+        <v>7.599330040836727</v>
       </c>
       <c r="G14" t="n">
-        <v>933.1977306545044</v>
+        <v>1451.528652668741</v>
       </c>
     </row>
     <row r="15">
@@ -934,10 +934,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2572069754071907</v>
+        <v>0.4000268806279962</v>
       </c>
       <c r="G15" t="n">
-        <v>49.1326189705581</v>
+        <v>76.40922320067784</v>
       </c>
     </row>
     <row r="17">
@@ -1008,10 +1008,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>5.142572077878717</v>
+        <v>7.999356919261684</v>
       </c>
       <c r="G19" t="n">
-        <v>982.3303493708534</v>
+        <v>1527.937875448637</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.06233797469117312</t>
+          <t>0.777772895903665</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.06233797469117312</t>
+          <t>0.777772895903665</t>
         </is>
       </c>
     </row>
@@ -1196,262 +1196,394 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OA_used</t>
+          <t>OA_min</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.5000771514876508</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nonextract_to_aq</t>
+          <t>OA_used</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HNO3, Gd(NO3)3, H2O, Eu(NO3)3, Nd(NO3)3, I_aq, Sr(NO3)2, CsNO3, Sm(NO3)3</t>
+          <t>0.777876294822178</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nonextract_to_org</t>
+          <t>O_tot_required</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dodecane</t>
+          <t>7.99829360770462</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>required_recovery</t>
+          <t>nonextract_to_aq</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UO2(NO3)2:0.999</t>
+          <t>H2O, I_aq, HNO3, Nd(NO3)3, Eu(NO3)3, Sr(NO3)2, Gd(NO3)3, CsNO3, Sm(NO3)3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nonextract_to_org</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dodecane</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Inlets</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>org_scale_factor</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.9998670753702084</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>required_recovery</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>phase</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>T [K]</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>p [Pa]</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>F_total [mol/s]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>m_dot [g/s]</t>
+          <t>UO2(NO3)2:0.999</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aq_in</t>
+          <t>tbp_available</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>298.15</v>
-      </c>
-      <c r="E25" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F25" t="n">
-        <v>10.28355737225821</v>
-      </c>
-      <c r="G25" t="n">
-        <v>522.6517384058458</v>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>org_in</t>
+          <t>tbp_free_min</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>298.15</v>
-      </c>
-      <c r="E26" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5.142572077878717</v>
-      </c>
-      <c r="G26" t="n">
-        <v>982.3303493708534</v>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tbp_limited</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Outlets</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>tbp_required</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>tbp_species</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>phase</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>T [K]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>p [Pa]</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>F_total [mol/s]</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>m_dot [g/s]</t>
+          <t>TBP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>org_out</t>
+          <t>tbp_stoich</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>F8</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>298.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5.936393202473185</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1297.511879146651</v>
+          <t>U:2.0; Pu:2.0; Np:2.0; Tc:4.0</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>w_N</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>w_OA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Inlets</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T [K]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>p [Pa]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>F_total [mol/s]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>m_dot [g/s]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>aq_in</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.28358489969196</v>
+      </c>
+      <c r="G36" t="n">
+        <v>522.6522343125655</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>org_in</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.999356919261684</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1527.937875448637</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Outlets</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T [K]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>p [Pa]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>F_total [mol/s]</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>m_dot [g/s]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>org_out</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8.815229668061383</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1850.161475644985</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>aq_out</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>F17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D42" t="n">
         <v>298.15</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E42" t="n">
         <v>100000</v>
       </c>
-      <c r="F31" t="n">
-        <v>9.489736247663743</v>
-      </c>
-      <c r="G31" t="n">
-        <v>207.4702086300481</v>
+      <c r="F42" t="n">
+        <v>9.467712150892268</v>
+      </c>
+      <c r="G42" t="n">
+        <v>200.4286341162171</v>
       </c>
     </row>
   </sheetData>
@@ -1636,7 +1768,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.8789072026534464</t>
+          <t>2.8788983617769035</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1780,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.16151160970086895</t>
+          <t>0.1615121056906661</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1792,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:0.01764063822997675; Dodecane:0.0</t>
+          <t>TBP:0.002123047241076949; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1948,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>9.489736247663743</v>
+        <v>9.467712150892268</v>
       </c>
       <c r="G30" t="n">
-        <v>207.4702086300481</v>
+        <v>200.4286341162171</v>
       </c>
     </row>
     <row r="32">
@@ -1890,10 +2022,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G34" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="35">
@@ -1919,10 +2051,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01764063822997675</v>
+        <v>0.002123047241076949</v>
       </c>
       <c r="G35" t="n">
-        <v>4.698019492130949</v>
+        <v>0.565405695149131</v>
       </c>
     </row>
   </sheetData>
@@ -2103,10 +2235,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G15" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="17">
@@ -2177,10 +2309,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G19" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
   </sheetData>
@@ -2361,10 +2493,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G15" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="17">
@@ -2435,10 +2567,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G19" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
   </sheetData>
@@ -2587,7 +2719,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18.707253091953216</t>
+          <t>18.88683182709484</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2743,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18.707253091953216</t>
+          <t>18.88683182709484</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2875,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I_aq:0.00012740483886196325; Zircaloy:0.07181612038518236; HNO3:0.20525469004319266; H2O:8.768893531830408; TBP:0.0012088401682881103; UO2(NO3)2:0.01288215890857653; Pu(NO3)4:0.0662290529479808; Np(NO3)4:0.0036348164279218498; Am(NO3)4:0.0037075504151499483; Nd(NO3)3:0.1446291876837644; Sm(NO3)3:0.029144787999383737; Eu(NO3)3:0.00422113820453272; Gd(NO3)3:0.0024477615699715714; CsNO3:0.0984338887285743; Sr(NO3)2:0.024125585381023; HTcO4:0.03533909389471808</t>
+          <t>I_aq:0.00014940930013135044; Zircaloy:0.08421969197358602; HNO3:0.2036621057748839; H2O:8.766250726263989; TBP:0.0012077841297041532; UO2(NO3)2:0.01128440142114828; Pu(NO3)4:0.007502977768134204; Np(NO3)4:0.0004897449485566517; Am(NO3)4:0.004347892259645025; Nd(NO3)3:0.16960851646937192; Sm(NO3)3:0.0341784693294294; Eu(NO3)3:0.004950183293903352; Gd(NO3)3:0.0028705216091054874; CsNO3:0.11543469271271355; Sr(NO3)2:0.028292385589398023; HTcO4:0.03113960080370861</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2923,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.02175402779264175</t>
+          <t>0.022051858832175746</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2947,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HNO3:0.2597222464367912; H2O:0.19500080656781904</t>
+          <t>HNO3:0.26131483070511285; H2O:0.19767113956798</t>
         </is>
       </c>
     </row>
@@ -2899,10 +3031,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F38" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="G38" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="40">
@@ -2973,10 +3105,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F42" t="n">
-        <v>9.017372556429157</v>
+        <v>9.006603133378098</v>
       </c>
       <c r="G42" t="n">
-        <v>182.8936314151229</v>
+        <v>179.8362127293603</v>
       </c>
     </row>
     <row r="43">
@@ -3002,10 +3134,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4547230530046102</v>
+        <v>0.4589859702730928</v>
       </c>
       <c r="G43" t="n">
-        <v>19.87855772279435</v>
+        <v>20.02701569170773</v>
       </c>
     </row>
   </sheetData>
@@ -3202,7 +3334,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HNO3, H2O, AHA</t>
+          <t>H2O, AHA, HNO3</t>
         </is>
       </c>
     </row>
@@ -3298,10 +3430,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>5.936393202473185</v>
+        <v>8.815229668061383</v>
       </c>
       <c r="G24" t="n">
-        <v>1297.511879146651</v>
+        <v>1850.161475644985</v>
       </c>
     </row>
     <row r="25">
@@ -3327,10 +3459,10 @@
         <v>100000</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5936393202473185</v>
+        <v>0.8815229668061383</v>
       </c>
       <c r="G25" t="n">
-        <v>11.08762085644052</v>
+        <v>16.46453005862058</v>
       </c>
     </row>
     <row r="27">
@@ -3401,10 +3533,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="G29" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
     <row r="30">
@@ -3430,10 +3562,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5977910589810663</v>
+        <v>0.8914177864322125</v>
       </c>
       <c r="G30" t="n">
-        <v>12.89203903632143</v>
+        <v>20.98863404990027</v>
       </c>
     </row>
   </sheetData>
@@ -3630,7 +3762,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.01055166067154961</t>
+          <t>0.015668657554625782</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3774,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:9.292723108654603e-05; Dodecane:0.0</t>
+          <t>TBP:0.00014820592766551005; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -3798,10 +3930,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5977910589810663</v>
+        <v>0.8914177864322125</v>
       </c>
       <c r="G30" t="n">
-        <v>12.89203903632143</v>
+        <v>20.98863404990027</v>
       </c>
     </row>
     <row r="32">
@@ -3872,10 +4004,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G34" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="35">
@@ -3901,10 +4033,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>9.292723108654603e-05</v>
+        <v>0.0001482059276655101</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02474819432850677</v>
+        <v>0.03946990624402331</v>
       </c>
     </row>
   </sheetData>
@@ -4085,10 +4217,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G15" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="17">
@@ -4159,10 +4291,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G19" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
   </sheetData>
@@ -4343,10 +4475,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G15" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="17">
@@ -4417,10 +4549,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G19" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
   </sheetData>
@@ -4589,10 +4721,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>3.669566341355424</v>
+        <v>3.669566341355434</v>
       </c>
       <c r="G14" t="n">
-        <v>140.1870639088391</v>
+        <v>140.1870639088395</v>
       </c>
     </row>
     <row r="15">
@@ -4618,10 +4750,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>2.570568549995886</v>
+        <v>2.570568549995905</v>
       </c>
       <c r="G15" t="n">
-        <v>104.3582919498539</v>
+        <v>104.3582919498547</v>
       </c>
     </row>
     <row r="16">
@@ -4647,10 +4779,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>3.391854372286896</v>
+        <v>3.391881899720625</v>
       </c>
       <c r="G16" t="n">
-        <v>61.10425651674843</v>
+        <v>61.10475242346707</v>
       </c>
     </row>
     <row r="18">
@@ -4721,10 +4853,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G20" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
   </sheetData>
@@ -4873,7 +5005,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.43616678118616276</t>
+          <t>0.5179934354995488</t>
         </is>
       </c>
     </row>
@@ -4897,7 +5029,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.43616678118616276</t>
+          <t>0.5179934354995488</t>
         </is>
       </c>
     </row>
@@ -4933,7 +5065,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.002674050992105038</t>
+          <t>0.003970824174802425</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5161,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HNO3:0.003016555279403728; H2O:0.577769100444481; TBP:3.6003150822420275e-05; AcOH:0.006047184013843636; N2O:0.003023592006921818; UO2(NO3)2:0.004580895177378207; Pu(NO3)4:0.004318442692437219; Np(NO3)4:0.00019912059963605972; HTcO4:4.426388143260738e-05</t>
+          <t>HNO3:0.004952864901581989; H2O:0.8604849911895133; TBP:4.189765373346932e-05; AcOH:0.007034198146665872; N2O:0.003517099073332936; UO2(NO3)2:0.003589653876055085; Pu(NO3)4:0.012583188344167781; Np(NO3)4:0.0006506961063287761; HTcO4:0.0004004033003035702</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5209,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.013401360590391416</t>
+          <t>0.010493782161351528</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5233,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HNO3:0.002331546704806348; H2O:0.007848066826522282</t>
+          <t>HNO3:0.00298878344802286; H2O:0.009125503092217713</t>
         </is>
       </c>
     </row>
@@ -5185,10 +5317,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="G38" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="40">
@@ -5259,10 +5391,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5888555437147036</v>
+        <v>0.8811407060517076</v>
       </c>
       <c r="G42" t="n">
-        <v>12.59768812466117</v>
+        <v>20.62420100004125</v>
       </c>
     </row>
     <row r="43">
@@ -5288,10 +5420,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01017961353132863</v>
+        <v>0.01211428654024057</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2882983448430565</v>
+        <v>0.3527251608331186</v>
       </c>
     </row>
   </sheetData>
@@ -5464,10 +5596,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4547230530046102</v>
+        <v>0.4589859702730928</v>
       </c>
       <c r="G14" t="n">
-        <v>19.87855772279435</v>
+        <v>20.02701569170773</v>
       </c>
     </row>
     <row r="15">
@@ -5493,10 +5625,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01017961353132863</v>
+        <v>0.01211428654024057</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2882983448430565</v>
+        <v>0.3527251608331186</v>
       </c>
     </row>
     <row r="17">
@@ -5567,10 +5699,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G19" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
   </sheetData>
@@ -5751,10 +5883,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="G15" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
     <row r="17">
@@ -5825,10 +5957,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="G19" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
   </sheetData>
@@ -6009,10 +6141,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>3.698039182285167</v>
+        <v>5.48906740929065</v>
       </c>
       <c r="G15" t="n">
-        <v>66.65015797140518</v>
+        <v>98.93005236327481</v>
       </c>
     </row>
     <row r="17">
@@ -6083,10 +6215,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>3.698039182285167</v>
+        <v>5.48906740929065</v>
       </c>
       <c r="G19" t="n">
-        <v>66.65015797140518</v>
+        <v>98.93005236327481</v>
       </c>
     </row>
   </sheetData>
@@ -6223,7 +6355,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.6233797469117311</t>
+          <t>0.6233797469117313</t>
         </is>
       </c>
     </row>
@@ -6371,10 +6503,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="G24" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
     <row r="25">
@@ -6400,10 +6532,10 @@
         <v>100000</v>
       </c>
       <c r="F25" t="n">
-        <v>3.698039182285167</v>
+        <v>5.48906740929065</v>
       </c>
       <c r="G25" t="n">
-        <v>66.65015797140518</v>
+        <v>98.93005236327481</v>
       </c>
     </row>
     <row r="27">
@@ -6474,10 +6606,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>5.124080949041672</v>
+        <v>7.995957361229651</v>
       </c>
       <c r="G29" t="n">
-        <v>977.4108501237899</v>
+        <v>1527.036082899733</v>
       </c>
     </row>
     <row r="30">
@@ -6503,10 +6635,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>4.506199696982931</v>
+        <v>6.298444896496306</v>
       </c>
       <c r="G30" t="n">
-        <v>384.9467688143852</v>
+        <v>417.5313411172469</v>
       </c>
     </row>
   </sheetData>
@@ -6691,7 +6823,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.010001802126509281</t>
+          <t>0.01000180212650928</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6835,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.06661933097151333</t>
+          <t>0.09888429528172654</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:0.0006750684471292648; Dodecane:0.0</t>
+          <t>TBP:0.0010661654297401374; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -6871,10 +7003,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>4.506199696982931</v>
+        <v>6.298444896496306</v>
       </c>
       <c r="G30" t="n">
-        <v>384.9467688143852</v>
+        <v>417.5313411172469</v>
       </c>
     </row>
     <row r="32">
@@ -6945,10 +7077,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="G34" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
     <row r="35">
@@ -6974,10 +7106,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0006750684471292648</v>
+        <v>0.001066165429740137</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1797828787025716</v>
+        <v>0.283939044917534</v>
       </c>
     </row>
   </sheetData>
@@ -7158,10 +7290,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="G15" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
     <row r="17">
@@ -7232,10 +7364,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="G19" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
   </sheetData>
@@ -7468,10 +7600,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="G19" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
     <row r="21">
@@ -7542,10 +7674,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>3.328235264056651</v>
+        <v>4.940160668361585</v>
       </c>
       <c r="G23" t="n">
-        <v>59.98514217426467</v>
+        <v>89.03704712694733</v>
       </c>
     </row>
     <row r="24">
@@ -7571,10 +7703,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="G24" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
   </sheetData>
@@ -7755,10 +7887,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="G15" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
     <row r="17">
@@ -7829,10 +7961,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="G19" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
   </sheetData>
@@ -8125,10 +8257,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="G24" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
     <row r="26">
@@ -8199,10 +8331,10 @@
         <v>100000</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="G28" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
     <row r="29">
@@ -8228,10 +8360,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="G29" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
   </sheetData>
@@ -8428,10 +8560,10 @@
         <v>100000</v>
       </c>
       <c r="F17" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G17" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="19">
@@ -8502,10 +8634,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G21" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
   </sheetData>
@@ -8686,10 +8818,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="G15" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
     <row r="17">
@@ -8760,10 +8892,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="G19" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
   </sheetData>
@@ -8984,10 +9116,10 @@
         <v>100000</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="G18" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
     <row r="20">
@@ -9058,10 +9190,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2691435545138166</v>
+        <v>0.2692376327459722</v>
       </c>
       <c r="G22" t="n">
-        <v>226.5916894016277</v>
+        <v>226.6708937712012</v>
       </c>
     </row>
     <row r="23">
@@ -9087,10 +9219,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1345717772569083</v>
+        <v>0.1346188163729861</v>
       </c>
       <c r="G23" t="n">
-        <v>4.306027728666552</v>
+        <v>4.307532886302809</v>
       </c>
     </row>
   </sheetData>
@@ -9271,10 +9403,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G15" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="17">
@@ -9345,10 +9477,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G19" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
   </sheetData>
@@ -9529,10 +9661,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G15" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="17">
@@ -9603,10 +9735,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G19" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
   </sheetData>
@@ -9787,10 +9919,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="G15" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
     <row r="17">
@@ -9861,10 +9993,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="G19" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
   </sheetData>
@@ -10037,10 +10169,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="G14" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="15">
@@ -10066,10 +10198,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>3.328235264056651</v>
+        <v>4.940160668361585</v>
       </c>
       <c r="G15" t="n">
-        <v>59.98514217426467</v>
+        <v>89.03704712694733</v>
       </c>
     </row>
     <row r="16">
@@ -10095,10 +10227,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="G16" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
     <row r="18">
@@ -10169,10 +10301,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="G20" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
   </sheetData>
@@ -10353,10 +10485,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="G15" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
     <row r="17">
@@ -10427,10 +10559,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="G19" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
   </sheetData>
@@ -10627,10 +10759,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="G16" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
     <row r="18">
@@ -10701,10 +10833,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>4.162875217484488</v>
+        <v>5.960068763988501</v>
       </c>
       <c r="G20" t="n">
-        <v>86.81281546525963</v>
+        <v>119.3035611957149</v>
       </c>
     </row>
     <row r="21">
@@ -10730,10 +10862,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>2.018576658853624</v>
+        <v>2.019282245594792</v>
       </c>
       <c r="G21" t="n">
-        <v>87.20977853844848</v>
+        <v>87.24026242577914</v>
       </c>
     </row>
   </sheetData>
@@ -10906,10 +11038,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>2.018576658853624</v>
+        <v>2.019282245594792</v>
       </c>
       <c r="G14" t="n">
-        <v>87.20977853844848</v>
+        <v>87.24026242577914</v>
       </c>
     </row>
     <row r="15">
@@ -11038,10 +11170,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="G20" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
   </sheetData>
@@ -11222,10 +11354,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="G15" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
     <row r="17">
@@ -11296,10 +11428,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="G19" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
   </sheetData>
@@ -11480,10 +11612,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G15" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="17">
@@ -11554,10 +11686,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G19" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
   </sheetData>
@@ -11778,7 +11910,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.909700269382763</t>
+          <t>1.9102590940817668</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11922,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.0254061416716147</t>
+          <t>1.0255831028262994</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.2985396545934567</t>
+          <t>2.2990891655474774</t>
         </is>
       </c>
     </row>
@@ -11922,10 +12054,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="G30" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
     <row r="31">
@@ -11951,10 +12083,10 @@
         <v>100000</v>
       </c>
       <c r="F31" t="n">
-        <v>11.02532988163151</v>
+        <v>11.02690850495147</v>
       </c>
       <c r="G31" t="n">
-        <v>198.6213178175917</v>
+        <v>198.6497567167007</v>
       </c>
     </row>
     <row r="33">
@@ -12025,10 +12157,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>12.17459970892824</v>
+        <v>12.17645308772521</v>
       </c>
       <c r="G35" t="n">
-        <v>322.752802594084</v>
+        <v>322.8109175575095</v>
       </c>
     </row>
     <row r="36">
@@ -12054,10 +12186,10 @@
         <v>100000</v>
       </c>
       <c r="F36" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="G36" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
   </sheetData>
@@ -12226,10 +12358,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>12.17459970892824</v>
+        <v>12.17645308772521</v>
       </c>
       <c r="G14" t="n">
-        <v>322.752802594084</v>
+        <v>322.8109175575095</v>
       </c>
     </row>
     <row r="15">
@@ -12255,10 +12387,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>4.162875217484488</v>
+        <v>5.960068763988501</v>
       </c>
       <c r="G15" t="n">
-        <v>86.81281546525963</v>
+        <v>119.3035611957149</v>
       </c>
     </row>
     <row r="17">
@@ -12329,10 +12461,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="G19" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
   </sheetData>
@@ -12513,10 +12645,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="G15" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
     <row r="17">
@@ -12587,10 +12719,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="G19" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
   </sheetData>
@@ -12763,7 +12895,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.628729502530655</t>
+          <t>12.420889518643158</t>
         </is>
       </c>
     </row>
@@ -12859,10 +12991,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="G22" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
     <row r="24">
@@ -12933,10 +13065,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>10.62872950253066</v>
+        <v>12.42088951864316</v>
       </c>
       <c r="G26" t="n">
-        <v>191.4765619880898</v>
+        <v>223.7623246783565</v>
       </c>
     </row>
     <row r="27">
@@ -12962,10 +13094,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>5.708745423882072</v>
+        <v>5.715632333070551</v>
       </c>
       <c r="G27" t="n">
-        <v>218.0890560712539</v>
+        <v>218.3521540748678</v>
       </c>
     </row>
   </sheetData>
@@ -13074,7 +13206,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.35720266557971003</t>
+          <t>0.3579771882590512</t>
         </is>
       </c>
     </row>
@@ -13146,10 +13278,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.708745423882072</v>
+        <v>5.715632333070551</v>
       </c>
       <c r="G15" t="n">
-        <v>218.0890560712539</v>
+        <v>218.3521540748678</v>
       </c>
     </row>
     <row r="17">
@@ -13220,10 +13352,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>2.039179082526648</v>
+        <v>2.046065991715117</v>
       </c>
       <c r="G19" t="n">
-        <v>77.90199216241473</v>
+        <v>78.16509016602832</v>
       </c>
     </row>
     <row r="20">
@@ -13249,10 +13381,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>3.669566341355424</v>
+        <v>3.669566341355434</v>
       </c>
       <c r="G20" t="n">
-        <v>140.1870639088391</v>
+        <v>140.1870639088395</v>
       </c>
     </row>
   </sheetData>
@@ -13433,10 +13565,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="G15" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
     <row r="17">
@@ -13507,10 +13639,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="G19" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
   </sheetData>
@@ -13691,10 +13823,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="G15" t="n">
-        <v>1.699515759527298</v>
+        <v>1.699894105269323</v>
       </c>
     </row>
     <row r="17">
@@ -13765,10 +13897,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="G19" t="n">
-        <v>1.699515759527298</v>
+        <v>1.699894105269323</v>
       </c>
     </row>
   </sheetData>
@@ -14085,10 +14217,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="G26" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
     <row r="27">
@@ -14114,10 +14246,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="G27" t="n">
-        <v>1.699515759527298</v>
+        <v>1.699894105269323</v>
       </c>
     </row>
     <row r="29">
@@ -14188,10 +14320,10 @@
         <v>100000</v>
       </c>
       <c r="F31" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="G31" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
   </sheetData>
@@ -14372,10 +14504,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="G15" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
     <row r="17">
@@ -14446,10 +14578,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="G19" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
   </sheetData>
@@ -14670,10 +14802,10 @@
         <v>100000</v>
       </c>
       <c r="F18" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="G18" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
     <row r="20">
@@ -14744,10 +14876,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="G22" t="n">
-        <v>2.344837399413673</v>
+        <v>2.345359406485886</v>
       </c>
     </row>
     <row r="23">
@@ -14773,10 +14905,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>1.860689688234281</v>
+        <v>1.860713757638193</v>
       </c>
       <c r="G23" t="n">
-        <v>53.94229669442474</v>
+        <v>53.94296085610881</v>
       </c>
     </row>
   </sheetData>
@@ -15142,10 +15274,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="G29" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="30">
@@ -15274,10 +15406,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="G35" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="36">
@@ -15487,10 +15619,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="G15" t="n">
-        <v>226.9325984460697</v>
+        <v>226.9355339878783</v>
       </c>
     </row>
     <row r="17">
@@ -15561,10 +15693,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="G19" t="n">
-        <v>226.9325984460697</v>
+        <v>226.9355339878783</v>
       </c>
     </row>
   </sheetData>
@@ -15821,10 +15953,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>1.860689688234281</v>
+        <v>1.860713757638193</v>
       </c>
       <c r="G21" t="n">
-        <v>53.94229669442474</v>
+        <v>53.94296085610881</v>
       </c>
     </row>
     <row r="22">
@@ -15850,10 +15982,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="G22" t="n">
-        <v>226.9325984460697</v>
+        <v>226.9355339878783</v>
       </c>
     </row>
     <row r="24">
@@ -15924,10 +16056,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>12.60975505681996</v>
+        <v>12.6099208753328</v>
       </c>
       <c r="G26" t="n">
-        <v>227.1520576550174</v>
+        <v>227.1550420527761</v>
       </c>
     </row>
     <row r="27">
@@ -15953,10 +16085,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="G27" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
   </sheetData>
@@ -16141,10 +16273,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="G15" t="n">
-        <v>2.344837399413673</v>
+        <v>2.345359406485886</v>
       </c>
     </row>
     <row r="17">
@@ -16215,10 +16347,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.006508013875697122</v>
+        <v>0.006509462687998574</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1172418699706837</v>
+        <v>0.1172679703242943</v>
       </c>
     </row>
     <row r="20">
@@ -16244,10 +16376,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1236522636382453</v>
+        <v>0.1236797910719729</v>
       </c>
       <c r="G20" t="n">
-        <v>2.227595529442989</v>
+        <v>2.228091436161592</v>
       </c>
     </row>
   </sheetData>
@@ -16428,10 +16560,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="G15" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
     <row r="17">
@@ -16502,10 +16634,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="G19" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
     <row r="20">
@@ -16895,10 +17027,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="G30" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
     <row r="31">
@@ -16998,10 +17130,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>1.847261911140401</v>
+        <v>1.847283111895956</v>
       </c>
       <c r="G35" t="n">
-        <v>53.58302480351708</v>
+        <v>53.58364010925099</v>
       </c>
     </row>
     <row r="36">
@@ -17287,7 +17419,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&lt;process_sim.unitops.TSA.IdealTSAColumnEMM17 object at 0x0000018955AC5160&gt;</t>
+          <t>&lt;process_sim.unitops.TSA.IdealTSAColumnEMM17 object at 0x000001A3F5AC52B0&gt;</t>
         </is>
       </c>
     </row>
@@ -17699,10 +17831,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01764063822997675</v>
+        <v>0.002123047241076949</v>
       </c>
       <c r="G14" t="n">
-        <v>4.698019492130949</v>
+        <v>0.565405695149131</v>
       </c>
     </row>
     <row r="15">
@@ -17728,10 +17860,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.292723108654603e-05</v>
+        <v>0.0001482059276655101</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02474819432850677</v>
+        <v>0.03946990624402331</v>
       </c>
     </row>
     <row r="16">
@@ -17757,10 +17889,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006750684471292648</v>
+        <v>0.001066165429740137</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1797828787025716</v>
+        <v>0.283939044917534</v>
       </c>
     </row>
     <row r="18">
@@ -17831,10 +17963,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01840863390819256</v>
+        <v>0.003337418598482597</v>
       </c>
       <c r="G20" t="n">
-        <v>4.902550565162027</v>
+        <v>0.8888146463106883</v>
       </c>
     </row>
   </sheetData>
@@ -18007,10 +18139,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>5.124080949041672</v>
+        <v>7.995957361229651</v>
       </c>
       <c r="G14" t="n">
-        <v>977.4108501237899</v>
+        <v>1527.036082899733</v>
       </c>
     </row>
     <row r="15">
@@ -18036,10 +18168,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01840863390819256</v>
+        <v>0.003337418598482597</v>
       </c>
       <c r="G15" t="n">
-        <v>4.902550565162027</v>
+        <v>0.8888146463106883</v>
       </c>
     </row>
     <row r="17">
@@ -18110,10 +18242,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="G19" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
   </sheetData>
@@ -18294,10 +18426,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="G15" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
     <row r="17">
@@ -18368,10 +18500,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="G19" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
   </sheetData>
@@ -18556,10 +18688,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="G15" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
     <row r="17">
@@ -18630,10 +18762,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2571244791474933</v>
+        <v>0.3999647389914068</v>
       </c>
       <c r="G19" t="n">
-        <v>49.11567003444761</v>
+        <v>76.39624487730219</v>
       </c>
     </row>
     <row r="20">
@@ -18659,10 +18791,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>4.885365103802371</v>
+        <v>7.599330040836727</v>
       </c>
       <c r="G20" t="n">
-        <v>933.1977306545044</v>
+        <v>1451.528652668741</v>
       </c>
     </row>
   </sheetData>
@@ -19375,10 +19507,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="G15" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="17">
@@ -19449,10 +19581,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="G19" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
   </sheetData>
@@ -19649,10 +19781,10 @@
         <v>100000</v>
       </c>
       <c r="F17" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="G17" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="19">
@@ -19723,10 +19855,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="G21" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
   </sheetData>

--- a/flowsheet_units.xlsx
+++ b/flowsheet_units.xlsx
@@ -630,10 +630,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>3.268202108648652</v>
+        <v>3.268202108648653</v>
       </c>
       <c r="G14" t="n">
-        <v>58.87666098730547</v>
+        <v>58.87666098730549</v>
       </c>
     </row>
     <row r="15">
@@ -659,10 +659,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1236797910719729</v>
+        <v>0.1236863202675489</v>
       </c>
       <c r="G15" t="n">
-        <v>2.228091436161592</v>
+        <v>2.228209059619894</v>
       </c>
     </row>
     <row r="17">
@@ -733,10 +733,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>3.391881899720625</v>
+        <v>3.391888428916202</v>
       </c>
       <c r="G19" t="n">
-        <v>61.10475242346707</v>
+        <v>61.10487004692538</v>
       </c>
     </row>
   </sheetData>
@@ -905,10 +905,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>7.599330040836727</v>
+        <v>7.598257699584324</v>
       </c>
       <c r="G14" t="n">
-        <v>1451.528652668741</v>
+        <v>1451.174813270047</v>
       </c>
     </row>
     <row r="15">
@@ -934,10 +934,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4000268806279962</v>
+        <v>0.4000415759223812</v>
       </c>
       <c r="G15" t="n">
-        <v>76.40922320067784</v>
+        <v>76.41311769563822</v>
       </c>
     </row>
     <row r="17">
@@ -1008,10 +1008,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>7.999356919261684</v>
+        <v>7.99829927330985</v>
       </c>
       <c r="G19" t="n">
-        <v>1527.937875448637</v>
+        <v>1527.587930546114</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.777876294822178</t>
+          <t>0.7777729530212468</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.99829360770462</t>
+          <t>7.998298685935975</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2O, I_aq, HNO3, Nd(NO3)3, Eu(NO3)3, Sr(NO3)2, Gd(NO3)3, CsNO3, Sm(NO3)3</t>
+          <t>H2O, Gd(NO3)3, Sr(NO3)2, Nd(NO3)3, Sm(NO3)3, I_aq, CsNO3, Eu(NO3)3, HNO3</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.9998670753702084</t>
+          <t>0.9999999265626536</t>
         </is>
       </c>
     </row>
@@ -1448,10 +1448,10 @@
         <v>100000</v>
       </c>
       <c r="F36" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G36" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="37">
@@ -1477,10 +1477,10 @@
         <v>100000</v>
       </c>
       <c r="F37" t="n">
-        <v>7.999356919261684</v>
+        <v>7.99829927330985</v>
       </c>
       <c r="G37" t="n">
-        <v>1527.937875448637</v>
+        <v>1527.587930546114</v>
       </c>
     </row>
     <row r="39">
@@ -1551,10 +1551,10 @@
         <v>100000</v>
       </c>
       <c r="F41" t="n">
-        <v>8.815229668061383</v>
+        <v>8.81446244264343</v>
       </c>
       <c r="G41" t="n">
-        <v>1850.161475644985</v>
+        <v>1849.86483227907</v>
       </c>
     </row>
     <row r="42">
@@ -1580,10 +1580,10 @@
         <v>100000</v>
       </c>
       <c r="F42" t="n">
-        <v>9.467712150892268</v>
+        <v>9.467428259553966</v>
       </c>
       <c r="G42" t="n">
-        <v>200.4286341162171</v>
+        <v>200.3754502030685</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.8788983617769035</t>
+          <t>2.8788962648290553</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.1615121056906661</t>
+          <t>0.1615122233338297</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:0.002123047241076949; Dodecane:0.0</t>
+          <t>TBP:0.0021230484680991864; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -1948,10 +1948,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>9.467712150892268</v>
+        <v>9.467428259553966</v>
       </c>
       <c r="G30" t="n">
-        <v>200.4286341162171</v>
+        <v>200.3754502030685</v>
       </c>
     </row>
     <row r="32">
@@ -2022,10 +2022,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G34" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="35">
@@ -2051,10 +2051,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>0.002123047241076949</v>
+        <v>0.002123048468099186</v>
       </c>
       <c r="G35" t="n">
-        <v>0.565405695149131</v>
+        <v>0.5654060219272392</v>
       </c>
     </row>
   </sheetData>
@@ -2235,10 +2235,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G15" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="17">
@@ -2309,10 +2309,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G19" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
   </sheetData>
@@ -2493,10 +2493,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G15" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="17">
@@ -2567,10 +2567,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G19" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
   </sheetData>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18.88683182709484</t>
+          <t>18.894833778200933</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18.88683182709484</t>
+          <t>18.894833778200933</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I_aq:0.00014940930013135044; Zircaloy:0.08421969197358602; HNO3:0.2036621057748839; H2O:8.766250726263989; TBP:0.0012077841297041532; UO2(NO3)2:0.01128440142114828; Pu(NO3)4:0.007502977768134204; Np(NO3)4:0.0004897449485566517; Am(NO3)4:0.004347892259645025; Nd(NO3)3:0.16960851646937192; Sm(NO3)3:0.0341784693294294; Eu(NO3)3:0.004950183293903352; Gd(NO3)3:0.0028705216091054874; CsNO3:0.11543469271271355; Sr(NO3)2:0.028292385589398023; HTcO4:0.03113960080370861</t>
+          <t>I_aq:0.00015057084480767172; Zircaloy:0.08487443658966638; HNO3:0.20359154890717213; H2O:8.766137904851128; TBP:0.0012171761600726788; UO2(NO3)2:0.01103636146206179; Pu(NO3)4:0.007561307764161703; Np(NO3)4:0.0004935523463374533; Am(NO3)4:0.004381693844305212; Nd(NO3)3:0.17092709482554222; Sm(NO3)3:0.034444181163026825; Eu(NO3)3:0.004988667237317805; Gd(NO3)3:0.002892837750673586; CsNO3:0.11633211042811252; Sr(NO3)2:0.028512337559140892; HTcO4:0.027763429346169603</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.022051858832175746</t>
+          <t>0.02206515731274</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HNO3:0.26131483070511285; H2O:0.19767113956798</t>
+          <t>HNO3:0.26138538757282637; H2O:0.1977904901764198</t>
         </is>
       </c>
     </row>
@@ -3031,10 +3031,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F38" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="G38" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="40">
@@ -3105,10 +3105,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F42" t="n">
-        <v>9.006603133378098</v>
+        <v>9.00612933333662</v>
       </c>
       <c r="G42" t="n">
-        <v>179.8362127293603</v>
+        <v>179.7764324588741</v>
       </c>
     </row>
     <row r="43">
@@ -3134,10 +3134,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4589859702730928</v>
+        <v>0.4591758777492462</v>
       </c>
       <c r="G43" t="n">
-        <v>20.02701569170773</v>
+        <v>20.03361172226714</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2O, AHA, HNO3</t>
+          <t>H2O, HNO3, AHA</t>
         </is>
       </c>
     </row>
@@ -3430,10 +3430,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>8.815229668061383</v>
+        <v>8.81446244264343</v>
       </c>
       <c r="G24" t="n">
-        <v>1850.161475644985</v>
+        <v>1849.86483227907</v>
       </c>
     </row>
     <row r="25">
@@ -3459,10 +3459,10 @@
         <v>100000</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8815229668061383</v>
+        <v>0.881446244264343</v>
       </c>
       <c r="G25" t="n">
-        <v>16.46453005862058</v>
+        <v>16.46309708336851</v>
       </c>
     </row>
     <row r="27">
@@ -3533,10 +3533,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="G29" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
     <row r="30">
@@ -3562,10 +3562,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8914177864322125</v>
+        <v>0.8913334180503505</v>
       </c>
       <c r="G30" t="n">
-        <v>20.98863404990027</v>
+        <v>20.98551975690453</v>
       </c>
     </row>
   </sheetData>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.015668657554625782</t>
+          <t>0.015667293847406148</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:0.00014820592766551005; Dodecane:0.0</t>
+          <t>TBP:0.0001482080801861594; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -3930,10 +3930,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8914177864322125</v>
+        <v>0.8913334180503505</v>
       </c>
       <c r="G30" t="n">
-        <v>20.98863404990027</v>
+        <v>20.98551975690453</v>
       </c>
     </row>
     <row r="32">
@@ -4004,10 +4004,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G34" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="35">
@@ -4033,10 +4033,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0001482059276655101</v>
+        <v>0.0001482080801861594</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03946990624402331</v>
+        <v>0.03947047949901761</v>
       </c>
     </row>
   </sheetData>
@@ -4217,10 +4217,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G15" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="17">
@@ -4291,10 +4291,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G19" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
   </sheetData>
@@ -4475,10 +4475,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G15" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="17">
@@ -4549,10 +4549,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G19" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
   </sheetData>
@@ -4721,10 +4721,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>3.669566341355434</v>
+        <v>3.669566341355437</v>
       </c>
       <c r="G14" t="n">
-        <v>140.1870639088395</v>
+        <v>140.1870639088396</v>
       </c>
     </row>
     <row r="15">
@@ -4750,10 +4750,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>2.570568549995905</v>
+        <v>2.570568549995908</v>
       </c>
       <c r="G15" t="n">
-        <v>104.3582919498547</v>
+        <v>104.3582919498548</v>
       </c>
     </row>
     <row r="16">
@@ -4779,10 +4779,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>3.391881899720625</v>
+        <v>3.391888428916202</v>
       </c>
       <c r="G16" t="n">
-        <v>61.10475242346707</v>
+        <v>61.10487004692538</v>
       </c>
     </row>
     <row r="18">
@@ -4853,10 +4853,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G20" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
   </sheetData>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.5179934354995488</t>
+          <t>0.5181816521948789</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.5179934354995488</t>
+          <t>0.5181816521948789</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.003970824174802425</t>
+          <t>0.003970478577767311</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HNO3:0.004952864901581989; H2O:0.8604849911895133; TBP:4.189765373346932e-05; AcOH:0.007034198146665872; N2O:0.003517099073332936; UO2(NO3)2:0.003589653876055085; Pu(NO3)4:0.012583188344167781; Np(NO3)4:0.0006506961063287761; HTcO4:0.0004004033003035702</t>
+          <t>HNO3:0.004951508560121844; H2O:0.8604056165107233; TBP:4.1910088026309376e-05; AcOH:0.007036281257711079; N2O:0.0035181406288555396; UO2(NO3)2:0.0035877360786312784; Pu(NO3)4:0.012588010321931856; Np(NO3)4:0.000650945458247389; HTcO4:0.0003903003550349055</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.010493782161351528</t>
+          <t>0.010498937973213883</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HNO3:0.00298878344802286; H2O:0.009125503092217713</t>
+          <t>HNO3:0.0029894485954127777; H2O:0.009129192020317811</t>
         </is>
       </c>
     </row>
@@ -5317,10 +5317,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F38" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="G38" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="40">
@@ -5391,10 +5391,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8811407060517076</v>
+        <v>0.8810518086433173</v>
       </c>
       <c r="G42" t="n">
-        <v>20.62420100004125</v>
+        <v>20.6209753492418</v>
       </c>
     </row>
     <row r="43">
@@ -5420,10 +5420,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01211428654024057</v>
+        <v>0.01211864061573059</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3527251608331186</v>
+        <v>0.3528335291401753</v>
       </c>
     </row>
   </sheetData>
@@ -5596,10 +5596,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4589859702730928</v>
+        <v>0.4591758777492462</v>
       </c>
       <c r="G14" t="n">
-        <v>20.02701569170773</v>
+        <v>20.03361172226714</v>
       </c>
     </row>
     <row r="15">
@@ -5625,10 +5625,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01211428654024057</v>
+        <v>0.01211864061573059</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3527251608331186</v>
+        <v>0.3528335291401753</v>
       </c>
     </row>
     <row r="17">
@@ -5699,10 +5699,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G19" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
   </sheetData>
@@ -5883,10 +5883,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="G15" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
     <row r="17">
@@ -5957,10 +5957,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="G19" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
   </sheetData>
@@ -6141,10 +6141,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.48906740929065</v>
+        <v>22.01143817214356</v>
       </c>
       <c r="G15" t="n">
-        <v>98.93005236327481</v>
+        <v>396.7145178934062</v>
       </c>
     </row>
     <row r="17">
@@ -6215,10 +6215,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>5.48906740929065</v>
+        <v>22.01143817214356</v>
       </c>
       <c r="G19" t="n">
-        <v>98.93005236327481</v>
+        <v>396.7145178934062</v>
       </c>
     </row>
   </sheetData>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.6233797469117313</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -6503,10 +6503,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="G24" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
     <row r="25">
@@ -6532,10 +6532,10 @@
         <v>100000</v>
       </c>
       <c r="F25" t="n">
-        <v>5.48906740929065</v>
+        <v>22.01143817214356</v>
       </c>
       <c r="G25" t="n">
-        <v>98.93005236327481</v>
+        <v>396.7145178934062</v>
       </c>
     </row>
     <row r="27">
@@ -6606,10 +6606,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>7.995957361229651</v>
+        <v>7.991618992392059</v>
       </c>
       <c r="G29" t="n">
-        <v>1527.036082899733</v>
+        <v>1525.808849165499</v>
       </c>
     </row>
     <row r="30">
@@ -6635,10 +6635,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>6.298444896496306</v>
+        <v>22.82439444860892</v>
       </c>
       <c r="G30" t="n">
-        <v>417.5313411172469</v>
+        <v>716.2480783334413</v>
       </c>
     </row>
   </sheetData>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.09888429528172654</t>
+          <t>0.3965310296801383</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TBP:0.0010661654297401374; Dodecane:0.0</t>
+          <t>TBP:0.004275750622102236; Dodecane:0.0</t>
         </is>
       </c>
     </row>
@@ -7003,10 +7003,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>6.298444896496306</v>
+        <v>22.82439444860892</v>
       </c>
       <c r="G30" t="n">
-        <v>417.5313411172469</v>
+        <v>716.2480783334413</v>
       </c>
     </row>
     <row r="32">
@@ -7077,10 +7077,10 @@
         <v>100000</v>
       </c>
       <c r="F34" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="G34" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
     <row r="35">
@@ -7106,10 +7106,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>0.001066165429740137</v>
+        <v>0.004275750622102236</v>
       </c>
       <c r="G35" t="n">
-        <v>0.283939044917534</v>
+        <v>1.138709354177023</v>
       </c>
     </row>
   </sheetData>
@@ -7290,10 +7290,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="G15" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
     <row r="17">
@@ -7364,10 +7364,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="G19" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
   </sheetData>
@@ -7600,10 +7600,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="G19" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
     <row r="21">
@@ -7674,10 +7674,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>4.940160668361585</v>
+        <v>19.8102943549292</v>
       </c>
       <c r="G23" t="n">
-        <v>89.03704712694733</v>
+        <v>357.0430661040656</v>
       </c>
     </row>
     <row r="24">
@@ -7703,10 +7703,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="G24" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
   </sheetData>
@@ -7887,10 +7887,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="G15" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
     <row r="17">
@@ -7961,10 +7961,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="G19" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
   </sheetData>
@@ -8257,10 +8257,10 @@
         <v>100000</v>
       </c>
       <c r="F24" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="G24" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
     <row r="26">
@@ -8331,10 +8331,10 @@
         <v>100000</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="G28" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
     <row r="29">
@@ -8360,10 +8360,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="G29" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
   </sheetData>
@@ -8560,10 +8560,10 @@
         <v>100000</v>
       </c>
       <c r="F17" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G17" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="19">
@@ -8634,10 +8634,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G21" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
   </sheetData>
@@ -8818,10 +8818,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="G15" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
     <row r="17">
@@ -8892,10 +8892,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="G19" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
   </sheetData>
@@ -9116,10 +9116,10 @@
         <v>100000</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="G18" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
     <row r="20">
@@ -9190,10 +9190,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2692376327459722</v>
+        <v>0.2692599470373526</v>
       </c>
       <c r="G22" t="n">
-        <v>226.6708937712012</v>
+        <v>226.6896801508001</v>
       </c>
     </row>
     <row r="23">
@@ -9219,10 +9219,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1346188163729861</v>
+        <v>0.1346299735186763</v>
       </c>
       <c r="G23" t="n">
-        <v>4.307532886302809</v>
+        <v>4.307889892650604</v>
       </c>
     </row>
   </sheetData>
@@ -9403,10 +9403,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G15" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="17">
@@ -9477,10 +9477,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G19" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
   </sheetData>
@@ -9661,10 +9661,10 @@
         <v>9332.565789473683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G15" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="17">
@@ -9735,10 +9735,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G19" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
   </sheetData>
@@ -9919,10 +9919,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="G15" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
     <row r="17">
@@ -9993,10 +9993,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="G19" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
   </sheetData>
@@ -10169,10 +10169,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="G14" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="15">
@@ -10198,10 +10198,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>4.940160668361585</v>
+        <v>19.8102943549292</v>
       </c>
       <c r="G15" t="n">
-        <v>89.03704712694733</v>
+        <v>357.0430661040656</v>
       </c>
     </row>
     <row r="16">
@@ -10227,10 +10227,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="G16" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
     <row r="18">
@@ -10301,10 +10301,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="G20" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
   </sheetData>
@@ -10485,10 +10485,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="G15" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
     <row r="17">
@@ -10559,10 +10559,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="G19" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
   </sheetData>
@@ -10759,10 +10759,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="G16" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
     <row r="18">
@@ -10833,10 +10833,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>5.960068763988501</v>
+        <v>22.48233608801895</v>
       </c>
       <c r="G20" t="n">
-        <v>119.3035611957149</v>
+        <v>417.0759724287396</v>
       </c>
     </row>
     <row r="21">
@@ -10862,10 +10862,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>2.019282245594792</v>
+        <v>2.019449602780145</v>
       </c>
       <c r="G21" t="n">
-        <v>87.24026242577914</v>
+        <v>87.24749285867227</v>
       </c>
     </row>
   </sheetData>
@@ -11038,10 +11038,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>2.019282245594792</v>
+        <v>2.019449602780145</v>
       </c>
       <c r="G14" t="n">
-        <v>87.24026242577914</v>
+        <v>87.24749285867227</v>
       </c>
     </row>
     <row r="15">
@@ -11170,10 +11170,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="G20" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
   </sheetData>
@@ -11354,10 +11354,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="G15" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
     <row r="17">
@@ -11428,10 +11428,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="G19" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
   </sheetData>
@@ -11612,10 +11612,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G15" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="17">
@@ -11686,10 +11686,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G19" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
   </sheetData>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.9102590940817668</t>
+          <t>1.9103916409725665</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.0255831028262994</t>
+          <t>1.0256250760083858</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.2990891655474774</t>
+          <t>2.29921950332343</t>
         </is>
       </c>
     </row>
@@ -12054,10 +12054,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="G30" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
     <row r="31">
@@ -12083,10 +12083,10 @@
         <v>100000</v>
       </c>
       <c r="F31" t="n">
-        <v>11.02690850495147</v>
+        <v>11.02728293652756</v>
       </c>
       <c r="G31" t="n">
-        <v>198.6497567167007</v>
+        <v>198.6565021015439</v>
       </c>
     </row>
     <row r="33">
@@ -12157,10 +12157,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>12.17645308772521</v>
+        <v>12.17689268818927</v>
       </c>
       <c r="G35" t="n">
-        <v>322.8109175575095</v>
+        <v>322.8247017687741</v>
       </c>
     </row>
     <row r="36">
@@ -12186,10 +12186,10 @@
         <v>100000</v>
       </c>
       <c r="F36" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="G36" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
   </sheetData>
@@ -12358,10 +12358,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>12.17645308772521</v>
+        <v>12.17689268818927</v>
       </c>
       <c r="G14" t="n">
-        <v>322.8109175575095</v>
+        <v>322.8247017687741</v>
       </c>
     </row>
     <row r="15">
@@ -12387,10 +12387,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.960068763988501</v>
+        <v>22.48233608801895</v>
       </c>
       <c r="G15" t="n">
-        <v>119.3035611957149</v>
+        <v>417.0759724287396</v>
       </c>
     </row>
     <row r="17">
@@ -12461,10 +12461,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="G19" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
   </sheetData>
@@ -12645,10 +12645,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="G15" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
     <row r="17">
@@ -12719,10 +12719,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="G19" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
   </sheetData>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12.420889518643158</t>
+          <t>28.937175172449805</t>
         </is>
       </c>
     </row>
@@ -12991,10 +12991,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="G22" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
     <row r="24">
@@ -13065,10 +13065,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>12.42088951864316</v>
+        <v>28.93717517244981</v>
       </c>
       <c r="G26" t="n">
-        <v>223.7623246783565</v>
+        <v>521.3032107316833</v>
       </c>
     </row>
     <row r="27">
@@ -13094,10 +13094,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>5.715632333070551</v>
+        <v>5.722053603758406</v>
       </c>
       <c r="G27" t="n">
-        <v>218.3521540748678</v>
+        <v>218.5974634658303</v>
       </c>
     </row>
   </sheetData>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.3579771882590512</t>
+          <t>0.35869766425376337</t>
         </is>
       </c>
     </row>
@@ -13278,10 +13278,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>5.715632333070551</v>
+        <v>5.722053603758406</v>
       </c>
       <c r="G15" t="n">
-        <v>218.3521540748678</v>
+        <v>218.5974634658303</v>
       </c>
     </row>
     <row r="17">
@@ -13352,10 +13352,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>2.046065991715117</v>
+        <v>2.05248726240297</v>
       </c>
       <c r="G19" t="n">
-        <v>78.16509016602832</v>
+        <v>78.41039955699071</v>
       </c>
     </row>
     <row r="20">
@@ -13381,10 +13381,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>3.669566341355434</v>
+        <v>3.669566341355437</v>
       </c>
       <c r="G20" t="n">
-        <v>140.1870639088395</v>
+        <v>140.1870639088396</v>
       </c>
     </row>
   </sheetData>
@@ -13565,10 +13565,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="G15" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
     <row r="17">
@@ -13639,10 +13639,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="G19" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
   </sheetData>
@@ -13823,10 +13823,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="G15" t="n">
-        <v>1.699894105269323</v>
+        <v>1.699983844595171</v>
       </c>
     </row>
     <row r="17">
@@ -13897,10 +13897,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="G19" t="n">
-        <v>1.699894105269323</v>
+        <v>1.699983844595171</v>
       </c>
     </row>
   </sheetData>
@@ -14217,10 +14217,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="G26" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
     <row r="27">
@@ -14246,10 +14246,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="G27" t="n">
-        <v>1.699894105269323</v>
+        <v>1.699983844595171</v>
       </c>
     </row>
     <row r="29">
@@ -14320,10 +14320,10 @@
         <v>100000</v>
       </c>
       <c r="F31" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="G31" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
   </sheetData>
@@ -14504,10 +14504,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="G15" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
     <row r="17">
@@ -14578,10 +14578,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="G19" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
   </sheetData>
@@ -14802,10 +14802,10 @@
         <v>100000</v>
       </c>
       <c r="F18" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="G18" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
     <row r="20">
@@ -14876,10 +14876,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="G22" t="n">
-        <v>2.345359406485886</v>
+        <v>2.34548322065252</v>
       </c>
     </row>
     <row r="23">
@@ -14905,10 +14905,10 @@
         <v>100000</v>
       </c>
       <c r="F23" t="n">
-        <v>1.860713757638193</v>
+        <v>1.860719466628253</v>
       </c>
       <c r="G23" t="n">
-        <v>53.94296085610881</v>
+        <v>53.9431183877397</v>
       </c>
     </row>
   </sheetData>
@@ -15274,10 +15274,10 @@
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="G29" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="30">
@@ -15406,10 +15406,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G35" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="36">
@@ -15619,10 +15619,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="G15" t="n">
-        <v>226.9355339878783</v>
+        <v>226.936230265155</v>
       </c>
     </row>
     <row r="17">
@@ -15693,10 +15693,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="G19" t="n">
-        <v>226.9355339878783</v>
+        <v>226.936230265155</v>
       </c>
     </row>
   </sheetData>
@@ -15953,10 +15953,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>1.860713757638193</v>
+        <v>1.860719466628253</v>
       </c>
       <c r="G21" t="n">
-        <v>53.94296085610881</v>
+        <v>53.9431183877397</v>
       </c>
     </row>
     <row r="22">
@@ -15982,10 +15982,10 @@
         <v>100000</v>
       </c>
       <c r="F22" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="G22" t="n">
-        <v>226.9355339878783</v>
+        <v>226.936230265155</v>
       </c>
     </row>
     <row r="24">
@@ -16056,10 +16056,10 @@
         <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>12.6099208753328</v>
+        <v>12.60996020560641</v>
       </c>
       <c r="G26" t="n">
-        <v>227.1550420527761</v>
+        <v>227.1557499181309</v>
       </c>
     </row>
     <row r="27">
@@ -16085,10 +16085,10 @@
         <v>100000</v>
       </c>
       <c r="F27" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="G27" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
   </sheetData>
@@ -16273,10 +16273,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="G15" t="n">
-        <v>2.345359406485886</v>
+        <v>2.34548322065252</v>
       </c>
     </row>
     <row r="17">
@@ -16347,10 +16347,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.006509462687998574</v>
+        <v>0.006509806329870996</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1172679703242943</v>
+        <v>0.117274161032626</v>
       </c>
     </row>
     <row r="20">
@@ -16376,10 +16376,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1236797910719729</v>
+        <v>0.1236863202675489</v>
       </c>
       <c r="G20" t="n">
-        <v>2.228091436161592</v>
+        <v>2.228209059619894</v>
       </c>
     </row>
   </sheetData>
@@ -16560,10 +16560,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="G15" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
     <row r="17">
@@ -16634,10 +16634,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="G19" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
     <row r="20">
@@ -17027,10 +17027,10 @@
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="G30" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
     <row r="31">
@@ -17130,10 +17130,10 @@
         <v>100000</v>
       </c>
       <c r="F35" t="n">
-        <v>1.847283111895956</v>
+        <v>1.847288140475108</v>
       </c>
       <c r="G35" t="n">
-        <v>53.58364010925099</v>
+        <v>53.58378605280372</v>
       </c>
     </row>
     <row r="36">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&lt;process_sim.unitops.TSA.IdealTSAColumnEMM17 object at 0x000001A3F5AC52B0&gt;</t>
+          <t>&lt;process_sim.unitops.TSA.IdealTSAColumnEMM17 object at 0x000001D05CF092B0&gt;</t>
         </is>
       </c>
     </row>
@@ -17831,10 +17831,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002123047241076949</v>
+        <v>0.002123048468099186</v>
       </c>
       <c r="G14" t="n">
-        <v>0.565405695149131</v>
+        <v>0.5654060219272392</v>
       </c>
     </row>
     <row r="15">
@@ -17860,10 +17860,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001482059276655101</v>
+        <v>0.0001482080801861594</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03946990624402331</v>
+        <v>0.03947047949901761</v>
       </c>
     </row>
     <row r="16">
@@ -17889,10 +17889,10 @@
         <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001066165429740137</v>
+        <v>0.004275750622102236</v>
       </c>
       <c r="G16" t="n">
-        <v>0.283939044917534</v>
+        <v>1.138709354177023</v>
       </c>
     </row>
     <row r="18">
@@ -17963,10 +17963,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.003337418598482597</v>
+        <v>0.006547007170387581</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8888146463106883</v>
+        <v>1.74358585560328</v>
       </c>
     </row>
   </sheetData>
@@ -18139,10 +18139,10 @@
         <v>100000</v>
       </c>
       <c r="F14" t="n">
-        <v>7.995957361229651</v>
+        <v>7.991618992392059</v>
       </c>
       <c r="G14" t="n">
-        <v>1527.036082899733</v>
+        <v>1525.808849165499</v>
       </c>
     </row>
     <row r="15">
@@ -18168,10 +18168,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003337418598482597</v>
+        <v>0.006547007170387581</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8888146463106883</v>
+        <v>1.74358585560328</v>
       </c>
     </row>
     <row r="17">
@@ -18242,10 +18242,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="G19" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
   </sheetData>
@@ -18426,10 +18426,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="G15" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
     <row r="17">
@@ -18500,10 +18500,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="G19" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
   </sheetData>
@@ -18688,10 +18688,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="G15" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
     <row r="17">
@@ -18762,10 +18762,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3999647389914068</v>
+        <v>0.3999082999781223</v>
       </c>
       <c r="G19" t="n">
-        <v>76.39624487730219</v>
+        <v>76.37762175105509</v>
       </c>
     </row>
     <row r="20">
@@ -18791,10 +18791,10 @@
         <v>100000</v>
       </c>
       <c r="F20" t="n">
-        <v>7.599330040836727</v>
+        <v>7.598257699584324</v>
       </c>
       <c r="G20" t="n">
-        <v>1451.528652668741</v>
+        <v>1451.174813270047</v>
       </c>
     </row>
   </sheetData>
@@ -19507,10 +19507,10 @@
         <v>100000</v>
       </c>
       <c r="F15" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G15" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="17">
@@ -19581,10 +19581,10 @@
         <v>100000</v>
       </c>
       <c r="F19" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G19" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
   </sheetData>
@@ -19781,10 +19781,10 @@
         <v>100000</v>
       </c>
       <c r="F17" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G17" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="19">
@@ -19855,10 +19855,10 @@
         <v>100000</v>
       </c>
       <c r="F21" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="G21" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
   </sheetData>
